--- a/saved_data/top_artist_carib_metrics_1_apr_2026.xlsx
+++ b/saved_data/top_artist_carib_metrics_1_apr_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Files\spotify_music_analysis\saved_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E67154-A049-4263-956C-4B12B5699E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3C3237-EB76-4BE7-869A-BFA0F20D3FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0C2FF910-49ED-45FA-A23C-1D15CC9ADB7F}"/>
+    <workbookView xWindow="10020" yWindow="130" windowWidth="9050" windowHeight="10070" xr2:uid="{0C2FF910-49ED-45FA-A23C-1D15CC9ADB7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>Country</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Suriname</t>
   </si>
   <si>
-    <t>Gente de Zona</t>
-  </si>
-  <si>
     <t>El Alfa</t>
   </si>
   <si>
@@ -129,12 +126,6 @@
     <t>Mighty Sparrow</t>
   </si>
   <si>
-    <t>sAINT JHN</t>
-  </si>
-  <si>
-    <t>Michael Brun</t>
-  </si>
-  <si>
     <t>Byron Messia</t>
   </si>
   <si>
@@ -148,6 +139,21 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>TikTok Followers</t>
+  </si>
+  <si>
+    <t>Instagram Followers</t>
+  </si>
+  <si>
+    <t>SAINt JHN</t>
+  </si>
+  <si>
+    <t>Michaël Brun</t>
+  </si>
+  <si>
+    <t>Gente De Zona</t>
   </si>
 </sst>
 </file>
@@ -513,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{999CDD1F-9799-49A3-94B5-D8F2FCE0D205}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.36328125" customWidth="1"/>
@@ -524,10 +530,11 @@
     <col min="6" max="6" width="22.6328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.81640625" customWidth="1"/>
+    <col min="9" max="9" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -552,10 +559,16 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -578,10 +591,16 @@
       <c r="H2">
         <v>239</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2">
+        <v>178000</v>
+      </c>
+      <c r="J2">
+        <v>2130000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -604,10 +623,16 @@
       <c r="H3">
         <v>248</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3">
+        <v>2000000</v>
+      </c>
+      <c r="J3">
+        <v>14500000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -630,10 +655,16 @@
       <c r="H4">
         <v>473</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4">
+        <v>42500</v>
+      </c>
+      <c r="J4">
+        <v>708000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -656,10 +687,16 @@
       <c r="H5">
         <v>575</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5">
+        <v>600000</v>
+      </c>
+      <c r="J5">
+        <v>3490000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -682,10 +719,16 @@
       <c r="H6">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6">
+        <v>520000</v>
+      </c>
+      <c r="J6">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -708,10 +751,16 @@
       <c r="H7">
         <v>121</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7">
+        <v>2230</v>
+      </c>
+      <c r="J7">
+        <v>6210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -734,10 +783,16 @@
       <c r="H8">
         <v>255</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8">
+        <v>181000</v>
+      </c>
+      <c r="J8">
+        <v>81900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -760,10 +815,16 @@
       <c r="H9">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
@@ -786,10 +847,16 @@
       <c r="H10">
         <v>161</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10">
+        <v>3700000</v>
+      </c>
+      <c r="J10">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -804,18 +871,24 @@
         <v>975000</v>
       </c>
       <c r="F11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>40</v>
-      </c>
-      <c r="G11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
@@ -838,10 +911,16 @@
       <c r="H12">
         <v>143</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12">
+        <v>699000</v>
+      </c>
+      <c r="J12">
+        <v>898000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
@@ -864,10 +943,16 @@
       <c r="H13">
         <v>379</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13">
+        <v>459000</v>
+      </c>
+      <c r="J13">
+        <v>267000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
@@ -890,10 +975,16 @@
       <c r="H14">
         <v>95</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14">
+        <v>187000</v>
+      </c>
+      <c r="J14">
+        <v>339000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
@@ -916,10 +1007,16 @@
       <c r="H15">
         <v>430</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" s="3">
+        <v>6980</v>
+      </c>
+      <c r="J15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -942,10 +1039,16 @@
       <c r="H16">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16">
+        <v>972000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
@@ -960,13 +1063,19 @@
         <v>13300000</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="I17">
+        <v>6010</v>
+      </c>
+      <c r="J17">
+        <v>35200</v>
       </c>
     </row>
   </sheetData>
